--- a/data/trans_orig/P19C03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C03-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>111505</t>
+          <t>112340</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146535</t>
+          <t>149436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107984</t>
+          <t>108001</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>143407</t>
+          <t>142311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>228107</t>
+          <t>231178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>280062</t>
+          <t>281391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>212866</t>
+          <t>209965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>247896</t>
+          <t>247061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232845</t>
+          <t>233941</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268268</t>
+          <t>268251</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>455591</t>
+          <t>454262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>507546</t>
+          <t>504475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,58%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>204541</t>
+          <t>203688</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>251075</t>
+          <t>254613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>192756</t>
+          <t>192777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>236980</t>
+          <t>241262</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>416022</t>
+          <t>411506</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>479529</t>
+          <t>480156</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>324706</t>
+          <t>321168</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371240</t>
+          <t>372093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>310728</t>
+          <t>306446</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354952</t>
+          <t>354931</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>643960</t>
+          <t>643333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>707467</t>
+          <t>711983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171542</t>
+          <t>171478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215731</t>
+          <t>217731</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>199271</t>
+          <t>199034</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>248950</t>
+          <t>250245</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>387410</t>
+          <t>387894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>451887</t>
+          <t>452612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>286161</t>
+          <t>284161</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>330350</t>
+          <t>330414</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>354615</t>
+          <t>353320</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>404294</t>
+          <t>404531</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>653570</t>
+          <t>652845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>718047</t>
+          <t>717563</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>122464</t>
+          <t>124132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161781</t>
+          <t>163587</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136517</t>
+          <t>134375</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172877</t>
+          <t>175023</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>266814</t>
+          <t>268411</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>325444</t>
+          <t>326369</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>242967</t>
+          <t>241161</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>282284</t>
+          <t>280616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>266308</t>
+          <t>264162</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>302668</t>
+          <t>304810</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>518489</t>
+          <t>517564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>577119</t>
+          <t>575522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43708</t>
+          <t>43186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70899</t>
+          <t>70181</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81422</t>
+          <t>80510</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114237</t>
+          <t>112703</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132477</t>
+          <t>131728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175478</t>
+          <t>175724</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201450</t>
+          <t>202168</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>228641</t>
+          <t>229163</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>204845</t>
+          <t>206379</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>237660</t>
+          <t>238572</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>415953</t>
+          <t>415707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>458954</t>
+          <t>459703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,73%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17976</t>
+          <t>18405</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>36673</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40465</t>
+          <t>38904</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63091</t>
+          <t>63208</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>62971</t>
+          <t>62472</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95051</t>
+          <t>93759</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176762</t>
+          <t>176092</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>194789</t>
+          <t>194360</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183847</t>
+          <t>183730</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>206473</t>
+          <t>208034</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>364652</t>
+          <t>365944</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>396732</t>
+          <t>397231</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,41%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14375</t>
+          <t>13965</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19446</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10616</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28226</t>
+          <t>29341</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112389</t>
+          <t>112799</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124110</t>
+          <t>124019</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>188762</t>
+          <t>188789</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>202544</t>
+          <t>202537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>306746</t>
+          <t>305631</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>324356</t>
+          <t>323695</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>738000</t>
+          <t>738252</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>835283</t>
+          <t>831122</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>825485</t>
+          <t>832173</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>928483</t>
+          <t>926843</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1595910</t>
+          <t>1600758</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1728616</t>
+          <t>1731109</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1618418</t>
+          <t>1622579</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1715701</t>
+          <t>1715449</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1812454</t>
+          <t>1814094</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1915452</t>
+          <t>1908764</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3466022</t>
+          <t>3463529</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3598728</t>
+          <t>3593880</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109496</t>
+          <t>110911</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147562</t>
+          <t>148738</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93628</t>
+          <t>92229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>128051</t>
+          <t>126879</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>210739</t>
+          <t>211067</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>262884</t>
+          <t>262580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>230700</t>
+          <t>229524</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268766</t>
+          <t>267351</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242940</t>
+          <t>244112</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277363</t>
+          <t>278762</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>486369</t>
+          <t>486673</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>538514</t>
+          <t>538186</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>182711</t>
+          <t>179848</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>230849</t>
+          <t>226996</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>167082</t>
+          <t>166339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>215462</t>
+          <t>212200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>361598</t>
+          <t>361545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>427151</t>
+          <t>425188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365465</t>
+          <t>369318</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413603</t>
+          <t>416466</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343348</t>
+          <t>346610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>391728</t>
+          <t>392471</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>727972</t>
+          <t>729935</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>793525</t>
+          <t>793578</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>175175</t>
+          <t>173624</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>222310</t>
+          <t>220524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210317</t>
+          <t>210684</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>261107</t>
+          <t>261171</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>398100</t>
+          <t>397833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>466836</t>
+          <t>465935</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>363420</t>
+          <t>365206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>410555</t>
+          <t>412106</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>398347</t>
+          <t>398283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>449137</t>
+          <t>448770</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>778348</t>
+          <t>779249</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>847084</t>
+          <t>847351</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155958</t>
+          <t>155014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202295</t>
+          <t>201663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148668</t>
+          <t>148861</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>195585</t>
+          <t>194272</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>319031</t>
+          <t>319389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>385633</t>
+          <t>384156</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340544</t>
+          <t>341176</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>386881</t>
+          <t>387825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>365843</t>
+          <t>367156</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>412760</t>
+          <t>412567</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>718634</t>
+          <t>720111</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>785236</t>
+          <t>784878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93343</t>
+          <t>93855</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>130191</t>
+          <t>128738</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104865</t>
+          <t>105103</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>145342</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>207827</t>
+          <t>208311</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>261091</t>
+          <t>263827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>231119</t>
+          <t>232572</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>267967</t>
+          <t>267455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>245666</t>
+          <t>245373</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>285850</t>
+          <t>285612</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>490934</t>
+          <t>488198</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>544198</t>
+          <t>543714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29558</t>
+          <t>29466</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57023</t>
+          <t>55788</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47618</t>
+          <t>47847</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74200</t>
+          <t>74818</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85306</t>
+          <t>86261</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123768</t>
+          <t>124954</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>205467</t>
+          <t>206702</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232932</t>
+          <t>233024</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>225393</t>
+          <t>224775</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251975</t>
+          <t>251746</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>438316</t>
+          <t>437130</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>476778</t>
+          <t>475823</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8402</t>
+          <t>8345</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23547</t>
+          <t>24306</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>13073</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30992</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>25450</t>
+          <t>24545</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49412</t>
+          <t>48496</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>161379</t>
+          <t>160620</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>176524</t>
+          <t>176581</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>272501</t>
+          <t>272912</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>290659</t>
+          <t>290420</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>439007</t>
+          <t>439923</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>462969</t>
+          <t>463874</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>819942</t>
+          <t>823239</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>925148</t>
+          <t>931331</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>850603</t>
+          <t>862414</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>961140</t>
+          <t>965794</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1714774</t>
+          <t>1714290</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1865452</t>
+          <t>1857413</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1986723</t>
+          <t>1980540</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2091929</t>
+          <t>2088632</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2183343</t>
+          <t>2178689</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2293880</t>
+          <t>2282069</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4190903</t>
+          <t>4198942</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4341581</t>
+          <t>4342065</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84739</t>
+          <t>84340</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121372</t>
+          <t>119900</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72585</t>
+          <t>74262</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105179</t>
+          <t>105480</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164890</t>
+          <t>165467</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>215172</t>
+          <t>212684</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>231468</t>
+          <t>232940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268101</t>
+          <t>268500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246751</t>
+          <t>246450</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279345</t>
+          <t>277668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>489598</t>
+          <t>492086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>539880</t>
+          <t>539303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,52%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148214</t>
+          <t>146448</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>190281</t>
+          <t>189915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130362</t>
+          <t>131303</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169794</t>
+          <t>171843</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>289932</t>
+          <t>287890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>350520</t>
+          <t>346398</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>302797</t>
+          <t>303163</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>344864</t>
+          <t>346630</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326926</t>
+          <t>324877</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>366358</t>
+          <t>365417</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>639277</t>
+          <t>643399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>699865</t>
+          <t>701907</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,91%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164802</t>
+          <t>164775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>209393</t>
+          <t>212426</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151582</t>
+          <t>150653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>194633</t>
+          <t>193911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>333028</t>
+          <t>330701</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>392650</t>
+          <t>392371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,69%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>348467</t>
+          <t>345434</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>393058</t>
+          <t>393085</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>378447</t>
+          <t>379169</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>421498</t>
+          <t>422427</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>738290</t>
+          <t>738569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>797912</t>
+          <t>800239</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120952</t>
+          <t>120614</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162450</t>
+          <t>162921</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136232</t>
+          <t>134673</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>179517</t>
+          <t>178156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>268674</t>
+          <t>271343</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330221</t>
+          <t>330903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>349922</t>
+          <t>349451</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>391420</t>
+          <t>391758</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>365367</t>
+          <t>366728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>408652</t>
+          <t>410211</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>727035</t>
+          <t>726353</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>788582</t>
+          <t>785913</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61552</t>
+          <t>61443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96560</t>
+          <t>92589</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79750</t>
+          <t>77786</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117316</t>
+          <t>114397</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>151778</t>
+          <t>152716</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>197272</t>
+          <t>203441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>274442</t>
+          <t>278413</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>309450</t>
+          <t>309559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>278557</t>
+          <t>281476</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>316123</t>
+          <t>318087</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>569603</t>
+          <t>563434</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>615097</t>
+          <t>614159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,09%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33245</t>
+          <t>33207</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55165</t>
+          <t>57489</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48495</t>
+          <t>47700</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74253</t>
+          <t>75201</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89199</t>
+          <t>87806</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>124365</t>
+          <t>124920</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>174960</t>
+          <t>172636</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196880</t>
+          <t>196918</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>202695</t>
+          <t>201747</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>228453</t>
+          <t>229248</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>382709</t>
+          <t>382154</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>417875</t>
+          <t>419268</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22456</t>
+          <t>22659</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17305</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41708</t>
+          <t>43218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31053</t>
+          <t>30601</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58575</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124601</t>
+          <t>124398</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137457</t>
+          <t>137962</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>186171</t>
+          <t>184661</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>210574</t>
+          <t>210086</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>316361</t>
+          <t>317555</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>343883</t>
+          <t>344335</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>683521</t>
+          <t>692520</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>780111</t>
+          <t>783155</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>707216</t>
+          <t>707993</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>799085</t>
+          <t>804134</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1419039</t>
+          <t>1416417</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1551376</t>
+          <t>1558872</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1884222</t>
+          <t>1881178</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1980812</t>
+          <t>1971813</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2068230</t>
+          <t>2063181</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2160099</t>
+          <t>2159322</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3980272</t>
+          <t>3972776</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4112609</t>
+          <t>4115231</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por un empaste en 2023 (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53211</t>
+          <t>54125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118063</t>
+          <t>114305</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33116</t>
+          <t>33861</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72409</t>
+          <t>73808</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101277</t>
+          <t>98413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>172372</t>
+          <t>168890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265384</t>
+          <t>269142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>330236</t>
+          <t>329322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231132</t>
+          <t>229733</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270425</t>
+          <t>269680</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514616</t>
+          <t>518098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>585711</t>
+          <t>588575</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,67%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73192</t>
+          <t>71338</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118780</t>
+          <t>115439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53656</t>
+          <t>51585</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108860</t>
+          <t>107789</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135386</t>
+          <t>137547</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>209989</t>
+          <t>210555</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>283571</t>
+          <t>286912</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>329159</t>
+          <t>331013</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>390832</t>
+          <t>391903</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>446036</t>
+          <t>448107</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>692053</t>
+          <t>691487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>766656</t>
+          <t>764495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,75%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97327</t>
+          <t>99294</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>138912</t>
+          <t>139681</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97699</t>
+          <t>97970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128338</t>
+          <t>128657</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>207041</t>
+          <t>203866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>254092</t>
+          <t>254333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>384033</t>
+          <t>383264</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>425618</t>
+          <t>423651</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>403543</t>
+          <t>403224</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>434182</t>
+          <t>433911</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>800735</t>
+          <t>800494</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>847786</t>
+          <t>850961</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,67%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57850</t>
+          <t>60669</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>198912</t>
+          <t>198129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136923</t>
+          <t>137526</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>271460</t>
+          <t>251296</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182928</t>
+          <t>182092</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>386440</t>
+          <t>389367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>664016</t>
+          <t>664799</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>805078</t>
+          <t>802259</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>429132</t>
+          <t>449296</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>563669</t>
+          <t>563066</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1177079</t>
+          <t>1174152</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1380591</t>
+          <t>1381427</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91342</t>
+          <t>88334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127924</t>
+          <t>123677</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98918</t>
+          <t>98706</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126093</t>
+          <t>126581</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>194206</t>
+          <t>193930</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>240578</t>
+          <t>239579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418655</t>
+          <t>422902</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>455237</t>
+          <t>458245</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>407790</t>
+          <t>407302</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>434965</t>
+          <t>435177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>839884</t>
+          <t>840883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>886256</t>
+          <t>886532</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37480</t>
+          <t>38370</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58953</t>
+          <t>59274</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22234</t>
+          <t>23887</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100416</t>
+          <t>101047</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>58350</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147323</t>
+          <t>147283</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>300400</t>
+          <t>300079</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>321873</t>
+          <t>320983</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>499493</t>
+          <t>498862</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>577675</t>
+          <t>576022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>811939</t>
+          <t>811979</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>900912</t>
+          <t>902121</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15646</t>
+          <t>15732</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30518</t>
+          <t>29024</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24854</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40615</t>
+          <t>39761</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44103</t>
+          <t>43611</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65273</t>
+          <t>65613</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245003</t>
+          <t>246497</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>259875</t>
+          <t>259789</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>368072</t>
+          <t>368926</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>383833</t>
+          <t>383882</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>618935</t>
+          <t>618595</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>640105</t>
+          <t>640597</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>466080</t>
+          <t>462873</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>677159</t>
+          <t>672309</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>518144</t>
+          <t>520003</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>714249</t>
+          <t>711757</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1057834</t>
+          <t>1075093</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1341274</t>
+          <t>1342961</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2675966</t>
+          <t>2680816</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2887045</t>
+          <t>2890252</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2863935</t>
+          <t>2866427</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3060040</t>
+          <t>3058181</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5590035</t>
+          <t>5588348</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5873475</t>
+          <t>5856216</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P19C03-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112340</t>
+          <t>113392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>149436</t>
+          <t>148558</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>108001</t>
+          <t>107025</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>142311</t>
+          <t>141389</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>231178</t>
+          <t>229436</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>281391</t>
+          <t>281899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>209965</t>
+          <t>210843</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>247061</t>
+          <t>246009</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,74%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>233941</t>
+          <t>234863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268251</t>
+          <t>269227</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>454262</t>
+          <t>453754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>504475</t>
+          <t>506217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203688</t>
+          <t>206725</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>254613</t>
+          <t>254466</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>192777</t>
+          <t>192235</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>241262</t>
+          <t>237636</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>411506</t>
+          <t>412950</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>480156</t>
+          <t>477920</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,54%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>321168</t>
+          <t>321315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>372093</t>
+          <t>369056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>306446</t>
+          <t>310072</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354931</t>
+          <t>355473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>643333</t>
+          <t>645569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>711983</t>
+          <t>710539</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,24%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171478</t>
+          <t>174531</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>217731</t>
+          <t>217750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>199034</t>
+          <t>200486</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>250245</t>
+          <t>247188</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>387894</t>
+          <t>385452</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>452612</t>
+          <t>451293</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,82%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>284161</t>
+          <t>284142</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>330414</t>
+          <t>327361</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>353320</t>
+          <t>356377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>404531</t>
+          <t>403079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652845</t>
+          <t>654164</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>717563</t>
+          <t>720005</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124132</t>
+          <t>124545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163587</t>
+          <t>163478</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134375</t>
+          <t>135024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>175023</t>
+          <t>174764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>268411</t>
+          <t>268888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>326369</t>
+          <t>323973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241161</t>
+          <t>241270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>280616</t>
+          <t>280203</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264162</t>
+          <t>264421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>304810</t>
+          <t>304161</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>517564</t>
+          <t>519960</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>575522</t>
+          <t>575045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>44643</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70181</t>
+          <t>71456</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80510</t>
+          <t>81188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112703</t>
+          <t>114716</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131728</t>
+          <t>131857</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175724</t>
+          <t>176199</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202168</t>
+          <t>200893</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>229163</t>
+          <t>227706</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>206379</t>
+          <t>204366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>238572</t>
+          <t>237894</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>415707</t>
+          <t>415232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>459703</t>
+          <t>459574</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18405</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36673</t>
+          <t>36883</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38904</t>
+          <t>39948</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63208</t>
+          <t>64525</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>62472</t>
+          <t>62242</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93759</t>
+          <t>92469</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176092</t>
+          <t>175882</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>194360</t>
+          <t>195017</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>183730</t>
+          <t>182413</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208034</t>
+          <t>206990</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>365944</t>
+          <t>367234</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>397231</t>
+          <t>397461</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>14053</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19419</t>
+          <t>20547</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>10763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29341</t>
+          <t>28979</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112799</t>
+          <t>112711</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>124019</t>
+          <t>123956</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>188789</t>
+          <t>187661</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>202537</t>
+          <t>202511</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>305631</t>
+          <t>305993</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>323695</t>
+          <t>324209</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>738252</t>
+          <t>736551</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>831122</t>
+          <t>833872</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>832173</t>
+          <t>826844</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>926843</t>
+          <t>928824</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1600758</t>
+          <t>1590088</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1731109</t>
+          <t>1727432</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1622579</t>
+          <t>1619829</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1715449</t>
+          <t>1717150</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1814094</t>
+          <t>1812113</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1908764</t>
+          <t>1914093</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3463529</t>
+          <t>3467206</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3593880</t>
+          <t>3604550</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>69,39%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>110911</t>
+          <t>109396</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>148738</t>
+          <t>147486</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92229</t>
+          <t>91527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126879</t>
+          <t>127343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>211067</t>
+          <t>211954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>262580</t>
+          <t>262712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>229524</t>
+          <t>230776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267351</t>
+          <t>268866</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>244112</t>
+          <t>243648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>278762</t>
+          <t>279464</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>486673</t>
+          <t>486541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>538186</t>
+          <t>537299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>179848</t>
+          <t>181891</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>226996</t>
+          <t>227841</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166339</t>
+          <t>166738</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>212200</t>
+          <t>214990</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>361545</t>
+          <t>358652</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>425188</t>
+          <t>427478</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369318</t>
+          <t>368473</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416466</t>
+          <t>414423</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346610</t>
+          <t>343820</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>392471</t>
+          <t>392072</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729935</t>
+          <t>727645</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>793578</t>
+          <t>796471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,95%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>173624</t>
+          <t>172194</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>220524</t>
+          <t>219603</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210684</t>
+          <t>211011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>261171</t>
+          <t>259418</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>397833</t>
+          <t>396699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>465935</t>
+          <t>464444</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,3%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>365206</t>
+          <t>366127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>412106</t>
+          <t>413536</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>398283</t>
+          <t>400036</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>448770</t>
+          <t>448443</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>779249</t>
+          <t>780740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>847351</t>
+          <t>848485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155014</t>
+          <t>157008</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>201663</t>
+          <t>202241</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148861</t>
+          <t>148815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>194272</t>
+          <t>193548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>319389</t>
+          <t>318204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>384156</t>
+          <t>385844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>341176</t>
+          <t>340598</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>387825</t>
+          <t>385831</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>367156</t>
+          <t>367880</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>412567</t>
+          <t>412613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>720111</t>
+          <t>718423</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>784878</t>
+          <t>786063</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,18%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93855</t>
+          <t>94055</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128738</t>
+          <t>130739</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105103</t>
+          <t>106391</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145342</t>
+          <t>144148</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>208311</t>
+          <t>208070</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>263827</t>
+          <t>260620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232572</t>
+          <t>230571</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>267455</t>
+          <t>267255</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>245373</t>
+          <t>246567</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>285612</t>
+          <t>284324</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>488198</t>
+          <t>491405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>543714</t>
+          <t>543955</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,33%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29466</t>
+          <t>30507</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55788</t>
+          <t>57387</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47847</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>74818</t>
+          <t>74921</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>86261</t>
+          <t>85092</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>124954</t>
+          <t>122932</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>206702</t>
+          <t>205103</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233024</t>
+          <t>231983</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224775</t>
+          <t>224672</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251746</t>
+          <t>251580</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>437130</t>
+          <t>439152</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>475823</t>
+          <t>476992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,86%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24306</t>
+          <t>24593</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30581</t>
+          <t>31518</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24545</t>
+          <t>24666</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48496</t>
+          <t>48827</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>160620</t>
+          <t>160333</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>176581</t>
+          <t>176547</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>272912</t>
+          <t>271975</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>290420</t>
+          <t>290681</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>439923</t>
+          <t>439592</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>463874</t>
+          <t>463753</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>823239</t>
+          <t>825376</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>931331</t>
+          <t>926135</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>862414</t>
+          <t>861046</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>965794</t>
+          <t>965161</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,47 +6163,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>30,69%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1683</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1785284</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>1709631</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>1859926</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>28,23%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>30,71%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1683</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1785284</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>1714290</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>1857413</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>28,31%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1980540</t>
+          <t>1985736</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2088632</t>
+          <t>2086495</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2178689</t>
+          <t>2179322</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2282069</t>
+          <t>2283437</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,47 +6276,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>69,31%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>72,62%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>3964</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>4271071</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>4196429</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>4346724</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>70,52%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>69,29%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>72,57%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>3964</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>4271071</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>4198942</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>4342065</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>70,52%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>69,33%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,77%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84340</t>
+          <t>85509</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119900</t>
+          <t>119716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74262</t>
+          <t>72579</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105480</t>
+          <t>104243</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165467</t>
+          <t>167383</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212684</t>
+          <t>216747</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>232940</t>
+          <t>233124</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>268500</t>
+          <t>267331</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246450</t>
+          <t>247687</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277668</t>
+          <t>279351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>492086</t>
+          <t>488023</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>539303</t>
+          <t>537387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,25%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>146448</t>
+          <t>148461</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>189915</t>
+          <t>190569</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131303</t>
+          <t>129806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>171843</t>
+          <t>170963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>287890</t>
+          <t>290213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>346398</t>
+          <t>350571</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,42%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>303163</t>
+          <t>302509</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>346630</t>
+          <t>344617</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324877</t>
+          <t>325757</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>365417</t>
+          <t>366914</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>643399</t>
+          <t>639226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>701907</t>
+          <t>699584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164775</t>
+          <t>164892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>212426</t>
+          <t>209500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>150653</t>
+          <t>149301</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193911</t>
+          <t>192831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>330701</t>
+          <t>330200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>392371</t>
+          <t>393652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>345434</t>
+          <t>348360</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>393085</t>
+          <t>392968</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>379169</t>
+          <t>380249</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>422427</t>
+          <t>423779</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>738569</t>
+          <t>737288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>800239</t>
+          <t>800740</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,8%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>120614</t>
+          <t>122601</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162921</t>
+          <t>165259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134673</t>
+          <t>134328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178156</t>
+          <t>177574</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>271343</t>
+          <t>266564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330903</t>
+          <t>327502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>349451</t>
+          <t>347113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>391758</t>
+          <t>389771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>366728</t>
+          <t>367310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>410211</t>
+          <t>410556</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>726353</t>
+          <t>729754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>785913</t>
+          <t>790692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,79%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61443</t>
+          <t>59718</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92589</t>
+          <t>92915</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77786</t>
+          <t>80249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114397</t>
+          <t>115930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152716</t>
+          <t>149782</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>203441</t>
+          <t>198973</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>278413</t>
+          <t>278087</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>309559</t>
+          <t>311284</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>281476</t>
+          <t>279943</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>318087</t>
+          <t>315624</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>563434</t>
+          <t>567902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>614159</t>
+          <t>617093</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33207</t>
+          <t>31240</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57489</t>
+          <t>56228</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47700</t>
+          <t>49395</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75201</t>
+          <t>75544</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87806</t>
+          <t>87723</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>124920</t>
+          <t>125048</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>172636</t>
+          <t>173897</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196918</t>
+          <t>198885</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201747</t>
+          <t>201404</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>229248</t>
+          <t>227553</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>382154</t>
+          <t>382026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>419268</t>
+          <t>419351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,7%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9095</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22659</t>
+          <t>21971</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17793</t>
+          <t>17424</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43218</t>
+          <t>41293</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30601</t>
+          <t>31293</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>58857</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124398</t>
+          <t>125086</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137962</t>
+          <t>137361</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>184661</t>
+          <t>186586</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>210086</t>
+          <t>210455</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>317555</t>
+          <t>316079</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>344335</t>
+          <t>343643</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>692520</t>
+          <t>684125</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>783155</t>
+          <t>781855</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>707993</t>
+          <t>707403</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>804134</t>
+          <t>799371</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1416417</t>
+          <t>1423747</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1558872</t>
+          <t>1555652</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1881178</t>
+          <t>1882478</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1971813</t>
+          <t>1980208</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2063181</t>
+          <t>2067944</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2159322</t>
+          <t>2159912</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3972776</t>
+          <t>3975996</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4115231</t>
+          <t>4107901</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,26%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>81833</t>
+          <t>86293</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54125</t>
+          <t>61335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114305</t>
+          <t>116268</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50110</t>
+          <t>56076</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33861</t>
+          <t>38360</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73808</t>
+          <t>79266</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>131943</t>
+          <t>142369</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98413</t>
+          <t>108649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168890</t>
+          <t>179087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>301614</t>
+          <t>292561</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269142</t>
+          <t>262586</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>329322</t>
+          <t>317519</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>253431</t>
+          <t>287164</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229733</t>
+          <t>263974</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>269680</t>
+          <t>304880</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>555045</t>
+          <t>579725</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>518098</t>
+          <t>543007</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>588575</t>
+          <t>613445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>84,95%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>383447</t>
+          <t>378854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>303541</t>
+          <t>343240</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>686988</t>
+          <t>722094</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92292</t>
+          <t>98361</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71338</t>
+          <t>77805</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115439</t>
+          <t>124191</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84982</t>
+          <t>96899</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51585</t>
+          <t>79846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107789</t>
+          <t>117029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>177273</t>
+          <t>195260</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137547</t>
+          <t>168837</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>210555</t>
+          <t>229523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>310059</t>
+          <t>347532</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>286912</t>
+          <t>321702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>331013</t>
+          <t>368088</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>414710</t>
+          <t>385710</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>391903</t>
+          <t>365580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>448107</t>
+          <t>402763</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>724769</t>
+          <t>733242</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>691487</t>
+          <t>698979</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>764495</t>
+          <t>759665</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>402351</t>
+          <t>445893</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>499692</t>
+          <t>482609</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>902042</t>
+          <t>928502</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,67 +10351,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>117448</t>
+          <t>128472</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99294</t>
+          <t>108632</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139681</t>
+          <t>151977</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>18,11%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>132254</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>115320</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>150176</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>21,78%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>18,99%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>112481</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>97970</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>128657</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,15%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>18,42%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>229929</t>
+          <t>260726</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>203866</t>
+          <t>234053</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>254333</t>
+          <t>290538</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -10464,69 +10464,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>405497</t>
+          <t>471453</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>383264</t>
+          <t>447948</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>423651</t>
+          <t>491293</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>81,89%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>475028</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>457106</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>491962</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>78,22%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>75,27%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>81,01%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>419400</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>403224</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>433911</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>78,85%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>75,81%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>81,58%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1054</t>
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>824898</t>
+          <t>946480</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>800494</t>
+          <t>916668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>850961</t>
+          <t>973153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>522945</t>
+          <t>599925</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>522945</t>
+          <t>599925</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>522945</t>
+          <t>599925</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>531881</t>
+          <t>607282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1054827</t>
+          <t>1207206</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1054827</t>
+          <t>1207206</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1054827</t>
+          <t>1207206</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>135098</t>
+          <t>149502</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60669</t>
+          <t>128786</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>198129</t>
+          <t>175082</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>169470</t>
+          <t>151075</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137526</t>
+          <t>134950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>251296</t>
+          <t>168495</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>304567</t>
+          <t>300577</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>182092</t>
+          <t>273250</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>389367</t>
+          <t>329686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>727830</t>
+          <t>528797</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>664799</t>
+          <t>503217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>802259</t>
+          <t>549513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>531122</t>
+          <t>570682</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449296</t>
+          <t>553262</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>563066</t>
+          <t>586807</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1258952</t>
+          <t>1099479</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1174152</t>
+          <t>1070370</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1381427</t>
+          <t>1126806</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>80,48%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>862928</t>
+          <t>678299</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>700592</t>
+          <t>721757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1563519</t>
+          <t>1400056</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>105855</t>
+          <t>109953</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88334</t>
+          <t>93407</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123677</t>
+          <t>129049</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>111830</t>
+          <t>124035</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98706</t>
+          <t>108906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126581</t>
+          <t>139427</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>217686</t>
+          <t>233989</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193930</t>
+          <t>211317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>239579</t>
+          <t>259518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>440724</t>
+          <t>483402</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422902</t>
+          <t>464306</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>458245</t>
+          <t>499948</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>422053</t>
+          <t>471146</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>407302</t>
+          <t>455754</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>435177</t>
+          <t>486275</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>862776</t>
+          <t>954547</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>840883</t>
+          <t>929018</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>886532</t>
+          <t>977219</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>546579</t>
+          <t>593355</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>533883</t>
+          <t>595181</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>533883</t>
+          <t>595181</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>533883</t>
+          <t>595181</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1080462</t>
+          <t>1188536</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1080462</t>
+          <t>1188536</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1080462</t>
+          <t>1188536</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47445</t>
+          <t>51773</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38370</t>
+          <t>40030</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59274</t>
+          <t>64985</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>63437</t>
+          <t>68067</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23887</t>
+          <t>56800</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101047</t>
+          <t>79539</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>110882</t>
+          <t>119840</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>106328</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147283</t>
+          <t>137426</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>311908</t>
+          <t>345971</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>300079</t>
+          <t>332759</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>320983</t>
+          <t>357714</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>536472</t>
+          <t>360858</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>498862</t>
+          <t>349386</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>576022</t>
+          <t>372125</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>848380</t>
+          <t>706829</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>811979</t>
+          <t>689243</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>902121</t>
+          <t>720341</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>359353</t>
+          <t>397744</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>599909</t>
+          <t>428925</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>959262</t>
+          <t>826669</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21718</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>17841</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29024</t>
+          <t>33623</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,67 +11758,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31856</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24805</t>
+          <t>28153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39761</t>
+          <t>44782</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>60629</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>49772</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>72809</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>9,73%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>53575</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>43611</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>65613</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>7,83%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>253803</t>
+          <t>277459</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>246497</t>
+          <t>268786</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>259789</t>
+          <t>284568</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,67 +11871,67 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>376831</t>
+          <t>410106</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>368926</t>
+          <t>401004</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>383882</t>
+          <t>417633</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>89,95%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>93,68%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1195</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>687567</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>675387</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>698424</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>91,9%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>90,27%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>93,93%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1195</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>630633</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>618595</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>640597</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>92,17%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>90,41%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>275521</t>
+          <t>302409</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>408687</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>684208</t>
+          <t>748196</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>601689</t>
+          <t>649304</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>462873</t>
+          <t>598651</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>672309</t>
+          <t>706277</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>624166</t>
+          <t>664087</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>520003</t>
+          <t>626031</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>711757</t>
+          <t>708473</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1225855</t>
+          <t>1313391</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1075093</t>
+          <t>1248757</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1342961</t>
+          <t>1387336</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2751436</t>
+          <t>2747175</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2680816</t>
+          <t>2690202</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2890252</t>
+          <t>2797828</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2954018</t>
+          <t>2960693</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2866427</t>
+          <t>2916307</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3058181</t>
+          <t>2998749</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5705454</t>
+          <t>5707868</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5588348</t>
+          <t>5633923</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5856216</t>
+          <t>5772502</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>82,21%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3353125</t>
+          <t>3396479</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3578184</t>
+          <t>3624780</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3578184</t>
+          <t>3624780</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3578184</t>
+          <t>3624780</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6931309</t>
+          <t>7021259</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6931309</t>
+          <t>7021259</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6931309</t>
+          <t>7021259</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
